--- a/forms/trg/Formulir_TRG_forestsociety.xlsx
+++ b/forms/trg/Formulir_TRG_forestsociety.xlsx
@@ -1593,7 +1593,11 @@
           <t>Mulyani Hasan, S.IP</t>
         </is>
       </c>
-      <c r="C26" s="12" t="n"/>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>Researcher</t>
+        </is>
+      </c>
       <c r="D26" s="12" t="n"/>
       <c r="E26" s="11" t="inlineStr">
         <is>
@@ -1626,7 +1630,11 @@
           <t>Rahmadi, S.IP</t>
         </is>
       </c>
-      <c r="C27" s="12" t="n"/>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>Researcher</t>
+        </is>
+      </c>
       <c r="D27" s="12" t="n"/>
       <c r="E27" s="11" t="inlineStr">
         <is>
@@ -1659,7 +1667,11 @@
           <t>Ibnu Hayat, S.E.</t>
         </is>
       </c>
-      <c r="C28" s="12" t="n"/>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>Researcher</t>
+        </is>
+      </c>
       <c r="D28" s="12" t="n"/>
       <c r="E28" s="11" t="inlineStr">
         <is>
@@ -1692,7 +1704,11 @@
           <t>Marsleni Caezaria, S.Hut</t>
         </is>
       </c>
-      <c r="C29" s="12" t="n"/>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>Researcher</t>
+        </is>
+      </c>
       <c r="D29" s="12" t="n"/>
       <c r="E29" s="11" t="inlineStr">
         <is>
@@ -1721,7 +1737,11 @@
           <t>Reski, S.P.</t>
         </is>
       </c>
-      <c r="C30" s="12" t="n"/>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>Researcher</t>
+        </is>
+      </c>
       <c r="D30" s="12" t="n"/>
       <c r="E30" s="11" t="inlineStr">
         <is>
@@ -1750,7 +1770,11 @@
           <t>Rezki Wahid, S.IP., M.Hut</t>
         </is>
       </c>
-      <c r="C31" s="12" t="n"/>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>Researcher</t>
+        </is>
+      </c>
       <c r="D31" s="12" t="n"/>
       <c r="E31" s="11" t="inlineStr">
         <is>
@@ -1779,7 +1803,11 @@
           <t>Djaelani Batara Wali, S.Hut</t>
         </is>
       </c>
-      <c r="C32" s="12" t="n"/>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>Researcher</t>
+        </is>
+      </c>
       <c r="D32" s="12" t="n"/>
       <c r="E32" s="11" t="inlineStr">
         <is>
@@ -1808,7 +1836,11 @@
           <t>Reymonset Tangke, S.Hut</t>
         </is>
       </c>
-      <c r="C33" s="12" t="n"/>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>Researcher</t>
+        </is>
+      </c>
       <c r="D33" s="12" t="n"/>
       <c r="E33" s="11" t="inlineStr">
         <is>
@@ -1837,7 +1869,11 @@
           <t>Firstly, S.Hut</t>
         </is>
       </c>
-      <c r="C34" s="12" t="n"/>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>Researcher</t>
+        </is>
+      </c>
       <c r="D34" s="12" t="n"/>
       <c r="E34" s="11" t="inlineStr">
         <is>
@@ -1866,7 +1902,11 @@
           <t>Shannon Chambers, M.A.</t>
         </is>
       </c>
-      <c r="C35" s="12" t="n"/>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>Researcher</t>
+        </is>
+      </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
           <t>PhD student in Geography at University of North Carolina - Chapel Hill</t>
@@ -1895,7 +1935,11 @@
           <t>Dalilah Haji Laidin, M.A.</t>
         </is>
       </c>
-      <c r="C36" s="12" t="n"/>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>Researcher</t>
+        </is>
+      </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
           <t>PhD student in Geography at University of Hawai'i at Manoa</t>
